--- a/erp-server/erp-server-wms/src/main/resources/excel/soReturnInstockError.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/soReturnInstockError.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <r>
       <rPr>
@@ -81,6 +81,9 @@
     <t>单据类型</t>
   </si>
   <si>
+    <t>退货物流单号</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -156,6 +159,9 @@
   </si>
   <si>
     <t>{.typeName}</t>
+  </si>
+  <si>
+    <t>{.returnLogisticCode}</t>
   </si>
   <si>
     <t>{.skuNo}</t>
@@ -1123,24 +1129,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="16.125" customWidth="1"/>
     <col min="2" max="2" width="16.5" customWidth="1"/>
     <col min="3" max="3" width="15.875" customWidth="1"/>
-    <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="14.25" customWidth="1"/>
-    <col min="6" max="6" width="14.625" customWidth="1"/>
-    <col min="7" max="7" width="23.25" customWidth="1"/>
-    <col min="8" max="8" width="17.75" customWidth="1"/>
-    <col min="9" max="9" width="17" customWidth="1"/>
-    <col min="10" max="10" width="12.375" customWidth="1"/>
-    <col min="11" max="11" width="13.375" customWidth="1"/>
-    <col min="12" max="12" width="18.375" customWidth="1"/>
+    <col min="4" max="5" width="17" customWidth="1"/>
+    <col min="6" max="6" width="14.25" customWidth="1"/>
+    <col min="7" max="7" width="14.625" customWidth="1"/>
+    <col min="8" max="8" width="23.25" customWidth="1"/>
+    <col min="9" max="9" width="17.75" customWidth="1"/>
+    <col min="10" max="10" width="17" customWidth="1"/>
+    <col min="11" max="11" width="12.375" customWidth="1"/>
+    <col min="12" max="12" width="13.375" customWidth="1"/>
+    <col min="13" max="13" width="18.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1153,13 +1159,13 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="H1" t="s">
@@ -1177,49 +1183,55 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M2" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="N2" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-wms/src/main/resources/excel/soReturnInstockError.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/soReturnInstockError.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <r>
       <rPr>
@@ -75,6 +75,28 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>退货类型</t>
+    </r>
+  </si>
+  <si>
     <t>入库日期</t>
   </si>
   <si>
@@ -153,6 +175,9 @@
   </si>
   <si>
     <t>{.warehouseName}</t>
+  </si>
+  <si>
+    <t>{.returnType}</t>
   </si>
   <si>
     <t>{.billDateStr}</t>
@@ -1129,31 +1154,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="16.125" customWidth="1"/>
     <col min="2" max="2" width="16.5" customWidth="1"/>
-    <col min="3" max="3" width="15.875" customWidth="1"/>
-    <col min="4" max="5" width="17" customWidth="1"/>
-    <col min="6" max="6" width="14.25" customWidth="1"/>
-    <col min="7" max="7" width="14.625" customWidth="1"/>
-    <col min="8" max="8" width="23.25" customWidth="1"/>
-    <col min="9" max="9" width="17.75" customWidth="1"/>
-    <col min="10" max="10" width="17" customWidth="1"/>
-    <col min="11" max="11" width="12.375" customWidth="1"/>
-    <col min="12" max="12" width="13.375" customWidth="1"/>
-    <col min="13" max="13" width="18.375" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="15.875" customWidth="1"/>
+    <col min="5" max="6" width="17" customWidth="1"/>
+    <col min="7" max="7" width="14.25" customWidth="1"/>
+    <col min="8" max="8" width="14.625" customWidth="1"/>
+    <col min="9" max="9" width="23.25" customWidth="1"/>
+    <col min="10" max="10" width="17.75" customWidth="1"/>
+    <col min="11" max="11" width="17" customWidth="1"/>
+    <col min="12" max="12" width="12.375" customWidth="1"/>
+    <col min="13" max="13" width="13.375" customWidth="1"/>
+    <col min="14" max="14" width="18.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
@@ -1162,13 +1188,13 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
@@ -1186,55 +1212,66 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N2" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="O2" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C1048576">
+      <formula1>"退货退款,退货补货"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
